--- a/data/trans_orig/P42A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P42A-Estudios-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72170</t>
+          <t>70554</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>105428</t>
+          <t>104135</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72170</t>
+          <t>70554</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>105428</t>
+          <t>104135</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61140</t>
+          <t>60624</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92874</t>
+          <t>91283</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61140</t>
+          <t>60624</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92874</t>
+          <t>91283</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76508</t>
+          <t>75110</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>109925</t>
+          <t>107376</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>76508</t>
+          <t>75110</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>109925</t>
+          <t>107376</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60867</t>
+          <t>61979</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91926</t>
+          <t>93263</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60867</t>
+          <t>61979</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91926</t>
+          <t>93263</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,34%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41132</t>
+          <t>41046</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67407</t>
+          <t>67908</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41132</t>
+          <t>41046</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67407</t>
+          <t>67908</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>101052</t>
+          <t>100372</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>141145</t>
+          <t>140706</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101052</t>
+          <t>100372</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>141145</t>
+          <t>140706</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82842</t>
+          <t>83066</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>119955</t>
+          <t>121497</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82842</t>
+          <t>83066</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>119955</t>
+          <t>121497</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>99808</t>
+          <t>99442</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>137063</t>
+          <t>138473</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>99808</t>
+          <t>99442</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>137063</t>
+          <t>138473</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87958</t>
+          <t>87164</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125325</t>
+          <t>124713</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1394,12 +1394,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87958</t>
+          <t>87164</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125325</t>
+          <t>124713</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75275</t>
+          <t>76185</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>109599</t>
+          <t>110392</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75275</t>
+          <t>76185</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>109599</t>
+          <t>110392</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1507,12 +1507,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27080</t>
+          <t>28079</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50098</t>
+          <t>50213</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27080</t>
+          <t>28079</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50098</t>
+          <t>50213</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19977</t>
+          <t>20023</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39133</t>
+          <t>38326</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19977</t>
+          <t>20023</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39133</t>
+          <t>38326</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -1773,12 +1773,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31771</t>
+          <t>32737</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55110</t>
+          <t>55805</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31771</t>
+          <t>32737</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55110</t>
+          <t>55805</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24057</t>
+          <t>24815</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45253</t>
+          <t>45588</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24057</t>
+          <t>24815</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45253</t>
+          <t>45588</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19662</t>
+          <t>20173</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38619</t>
+          <t>40221</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19662</t>
+          <t>20173</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38619</t>
+          <t>40221</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1979,12 +1979,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>216668</t>
+          <t>217163</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>272275</t>
+          <t>272518</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>216668</t>
+          <t>217163</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>272275</t>
+          <t>272518</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -2167,12 +2167,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>179079</t>
+          <t>179454</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>230349</t>
+          <t>229013</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>179079</t>
+          <t>179454</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>230349</t>
+          <t>229013</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -2245,12 +2245,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>226004</t>
+          <t>225706</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282251</t>
+          <t>282422</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>226004</t>
+          <t>225706</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>282251</t>
+          <t>282422</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>188269</t>
+          <t>186685</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>239937</t>
+          <t>239848</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>188269</t>
+          <t>186685</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>239937</t>
+          <t>239848</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -2401,12 +2401,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>152302</t>
+          <t>149703</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>199774</t>
+          <t>197687</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>152302</t>
+          <t>149703</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>199774</t>
+          <t>197687</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -2731,12 +2731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>137135</t>
+          <t>139124</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>186817</t>
+          <t>185280</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>137135</t>
+          <t>139124</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>186817</t>
+          <t>185280</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -2809,12 +2809,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>381834</t>
+          <t>379031</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>447985</t>
+          <t>445269</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>381834</t>
+          <t>379031</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>447985</t>
+          <t>445269</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,19%</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>249446</t>
+          <t>248621</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311706</t>
+          <t>307364</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>249446</t>
+          <t>248621</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>311706</t>
+          <t>307364</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>144179</t>
+          <t>144233</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>195448</t>
+          <t>197167</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>144179</t>
+          <t>144233</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>195448</t>
+          <t>197167</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -3043,12 +3043,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>93964</t>
+          <t>95029</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>137230</t>
+          <t>137180</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>93964</t>
+          <t>95029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>137230</t>
+          <t>137180</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>130401</t>
+          <t>130819</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>179208</t>
+          <t>179395</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>130401</t>
+          <t>130819</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>179208</t>
+          <t>179395</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -3281,12 +3281,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>193501</t>
+          <t>194039</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>249910</t>
+          <t>250797</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>193501</t>
+          <t>194039</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>249910</t>
+          <t>250797</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>451933</t>
+          <t>451905</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>532513</t>
+          <t>528094</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>451933</t>
+          <t>451905</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>532513</t>
+          <t>528094</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -3437,12 +3437,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>329494</t>
+          <t>329535</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>399659</t>
+          <t>401191</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>329494</t>
+          <t>329535</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>399659</t>
+          <t>401191</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3487,12 +3487,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -3515,12 +3515,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>259565</t>
+          <t>263123</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>322969</t>
+          <t>330782</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>259565</t>
+          <t>263123</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>322969</t>
+          <t>330782</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -3675,12 +3675,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7989</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23071</t>
+          <t>22794</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7989</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23071</t>
+          <t>22794</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -3753,12 +3753,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28165</t>
+          <t>29120</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55719</t>
+          <t>55098</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3788,12 +3788,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28165</t>
+          <t>29120</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55719</t>
+          <t>55098</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3803,12 +3803,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -3831,12 +3831,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>124198</t>
+          <t>122801</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>166357</t>
+          <t>167172</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -3866,12 +3866,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>124198</t>
+          <t>122801</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166357</t>
+          <t>167172</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -3881,12 +3881,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,68%</t>
         </is>
       </c>
     </row>
@@ -3909,12 +3909,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>103964</t>
+          <t>103671</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>144017</t>
+          <t>145222</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3924,12 +3924,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>103964</t>
+          <t>103671</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>144017</t>
+          <t>145222</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,47%</t>
         </is>
       </c>
     </row>
@@ -3987,12 +3987,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>80441</t>
+          <t>79607</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>116959</t>
+          <t>117161</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>80441</t>
+          <t>79607</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>116959</t>
+          <t>117161</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>294763</t>
+          <t>294607</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>363195</t>
+          <t>364942</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>294763</t>
+          <t>294607</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>363195</t>
+          <t>364942</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -4225,12 +4225,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>626824</t>
+          <t>630287</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>722505</t>
+          <t>724331</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>626824</t>
+          <t>630287</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>722505</t>
+          <t>724331</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -4303,12 +4303,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>860992</t>
+          <t>860757</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>964949</t>
+          <t>967034</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>860992</t>
+          <t>860757</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>964949</t>
+          <t>967034</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,41%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>610251</t>
+          <t>610787</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>706375</t>
+          <t>703856</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>610251</t>
+          <t>610787</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>706375</t>
+          <t>703856</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -4459,12 +4459,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>463902</t>
+          <t>463199</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>544572</t>
+          <t>548847</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4474,12 +4474,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>463902</t>
+          <t>463199</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>544572</t>
+          <t>548847</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -4789,12 +4789,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>100093</t>
+          <t>102032</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142319</t>
+          <t>147046</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4804,12 +4804,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100093</t>
+          <t>102032</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>142319</t>
+          <t>147046</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -4867,12 +4867,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>306925</t>
+          <t>306384</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>367352</t>
+          <t>366569</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4882,12 +4882,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>306925</t>
+          <t>306384</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>367352</t>
+          <t>366569</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,37%</t>
         </is>
       </c>
     </row>
@@ -4945,12 +4945,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>204513</t>
+          <t>202580</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>260385</t>
+          <t>258477</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4960,12 +4960,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4980,12 +4980,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>204513</t>
+          <t>202580</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>260385</t>
+          <t>258477</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4995,12 +4995,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,29%</t>
         </is>
       </c>
     </row>
@@ -5023,12 +5023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65956</t>
+          <t>64814</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>99613</t>
+          <t>100604</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5058,12 +5058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65956</t>
+          <t>64814</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>99613</t>
+          <t>100604</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5073,12 +5073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -5101,12 +5101,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41122</t>
+          <t>40840</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>70527</t>
+          <t>71015</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41122</t>
+          <t>40840</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>70527</t>
+          <t>71015</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -5261,12 +5261,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91538</t>
+          <t>90127</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>132356</t>
+          <t>132887</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5276,12 +5276,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91538</t>
+          <t>90127</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>132356</t>
+          <t>132887</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -5339,12 +5339,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312046</t>
+          <t>310702</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>380762</t>
+          <t>377348</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>312046</t>
+          <t>310702</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>380762</t>
+          <t>377348</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5389,12 +5389,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -5417,12 +5417,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>651110</t>
+          <t>655311</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>734296</t>
+          <t>738872</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5452,12 +5452,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>651110</t>
+          <t>655311</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>734296</t>
+          <t>738872</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,93%</t>
         </is>
       </c>
     </row>
@@ -5495,12 +5495,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>294326</t>
+          <t>296875</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>362926</t>
+          <t>360636</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>294326</t>
+          <t>296875</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>362926</t>
+          <t>360636</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -5573,12 +5573,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214714</t>
+          <t>216916</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>273931</t>
+          <t>277094</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>214714</t>
+          <t>216916</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>273931</t>
+          <t>277094</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -5733,12 +5733,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12079</t>
+          <t>11718</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30063</t>
+          <t>30900</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5748,12 +5748,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12079</t>
+          <t>11718</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30063</t>
+          <t>30900</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -5811,12 +5811,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45253</t>
+          <t>46124</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76813</t>
+          <t>77683</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45253</t>
+          <t>46124</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76813</t>
+          <t>77683</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -5889,12 +5889,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>159388</t>
+          <t>158020</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>203314</t>
+          <t>201679</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159388</t>
+          <t>158020</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>203314</t>
+          <t>201679</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,02%</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>132023</t>
+          <t>133375</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>170971</t>
+          <t>175504</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>132023</t>
+          <t>133375</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>170971</t>
+          <t>175504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,82%</t>
         </is>
       </c>
     </row>
@@ -6045,12 +6045,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75063</t>
+          <t>77483</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>110271</t>
+          <t>112040</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>75063</t>
+          <t>77483</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110271</t>
+          <t>112040</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -6205,12 +6205,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>221309</t>
+          <t>218065</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>288292</t>
+          <t>285279</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6220,12 +6220,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>221309</t>
+          <t>218065</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>288292</t>
+          <t>285279</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -6283,12 +6283,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>698399</t>
+          <t>691286</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>795630</t>
+          <t>791427</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6318,12 +6318,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>698399</t>
+          <t>691286</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>795630</t>
+          <t>791427</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6333,12 +6333,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -6361,12 +6361,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1053528</t>
+          <t>1047487</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1157094</t>
+          <t>1156618</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1053528</t>
+          <t>1047487</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1157094</t>
+          <t>1156618</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,91%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>522728</t>
+          <t>521866</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>605653</t>
+          <t>609635</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>522728</t>
+          <t>521866</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>605653</t>
+          <t>609635</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -6517,12 +6517,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>354131</t>
+          <t>355998</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>434387</t>
+          <t>433086</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6552,12 +6552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>354131</t>
+          <t>355998</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>434387</t>
+          <t>433086</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -6842,32 +6842,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>82132</t>
+          <t>91399</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69878</t>
+          <t>77892</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94862</t>
+          <t>104111</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6877,32 +6877,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>82132</t>
+          <t>91399</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69878</t>
+          <t>77892</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94862</t>
+          <t>104111</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -6920,32 +6920,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>265352</t>
+          <t>285567</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>248851</t>
+          <t>267351</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>283367</t>
+          <t>303131</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6955,32 +6955,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>265352</t>
+          <t>285567</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248851</t>
+          <t>267351</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283367</t>
+          <t>303131</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -6998,32 +6998,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>94537</t>
+          <t>100696</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>82062</t>
+          <t>87873</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112209</t>
+          <t>116183</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7033,32 +7033,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>94537</t>
+          <t>100696</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>82062</t>
+          <t>87873</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>112209</t>
+          <t>116183</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -7076,32 +7076,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51137</t>
+          <t>57903</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40061</t>
+          <t>46587</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62935</t>
+          <t>70977</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7111,32 +7111,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51137</t>
+          <t>57903</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40061</t>
+          <t>46587</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62935</t>
+          <t>70977</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -7154,32 +7154,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>22844</t>
+          <t>24194</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16240</t>
+          <t>17598</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30527</t>
+          <t>32685</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>22844</t>
+          <t>24194</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16240</t>
+          <t>17598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30527</t>
+          <t>32685</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>516002</t>
+          <t>559759</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>516002</t>
+          <t>559759</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>516002</t>
+          <t>559759</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516002</t>
+          <t>559759</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516002</t>
+          <t>559759</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516002</t>
+          <t>559759</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7314,32 +7314,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>103110</t>
+          <t>120038</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82660</t>
+          <t>101419</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>122668</t>
+          <t>141144</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7349,32 +7349,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>103110</t>
+          <t>120038</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82660</t>
+          <t>101419</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122668</t>
+          <t>141144</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -7392,32 +7392,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>432039</t>
+          <t>362257</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>361987</t>
+          <t>333048</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>572399</t>
+          <t>387036</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7427,32 +7427,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>432039</t>
+          <t>362257</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>361987</t>
+          <t>333048</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>572399</t>
+          <t>387036</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -7470,32 +7470,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>350607</t>
+          <t>392706</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>290391</t>
+          <t>366623</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>386055</t>
+          <t>424866</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7505,32 +7505,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>350607</t>
+          <t>392706</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>290391</t>
+          <t>366623</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>386055</t>
+          <t>424866</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>32,32%</t>
         </is>
       </c>
     </row>
@@ -7548,32 +7548,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>231685</t>
+          <t>257612</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>189420</t>
+          <t>233756</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>258924</t>
+          <t>287374</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7583,32 +7583,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>231685</t>
+          <t>257612</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>189420</t>
+          <t>233756</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>258924</t>
+          <t>287374</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -7626,32 +7626,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>164318</t>
+          <t>181752</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>135980</t>
+          <t>160510</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>189931</t>
+          <t>206603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7661,32 +7661,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>164318</t>
+          <t>181752</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>135980</t>
+          <t>160510</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>189931</t>
+          <t>206603</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -7704,17 +7704,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1281760</t>
+          <t>1314366</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1281760</t>
+          <t>1314366</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1281760</t>
+          <t>1314366</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7739,17 +7739,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1281760</t>
+          <t>1314366</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1281760</t>
+          <t>1314366</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1281760</t>
+          <t>1314366</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7786,32 +7786,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7051</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>4518</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>15500</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7821,32 +7821,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7051</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>4518</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>15500</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -7864,32 +7864,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>75814</t>
+          <t>85601</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64325</t>
+          <t>71687</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90721</t>
+          <t>100518</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7899,32 +7899,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>75814</t>
+          <t>85601</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64325</t>
+          <t>71687</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90721</t>
+          <t>100518</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -7942,32 +7942,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>132809</t>
+          <t>146685</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>117844</t>
+          <t>129080</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>150980</t>
+          <t>164303</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7977,32 +7977,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>132809</t>
+          <t>146685</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>117844</t>
+          <t>129080</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>150980</t>
+          <t>164303</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,03%</t>
         </is>
       </c>
     </row>
@@ -8020,17 +8020,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>115548</t>
+          <t>129002</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>100655</t>
+          <t>112782</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>132238</t>
+          <t>146509</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8055,17 +8055,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>115548</t>
+          <t>129002</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>100655</t>
+          <t>112782</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>132238</t>
+          <t>146509</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -8098,32 +8098,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>77192</t>
+          <t>86065</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62560</t>
+          <t>71985</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>92514</t>
+          <t>103238</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8133,32 +8133,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>77192</t>
+          <t>86065</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62560</t>
+          <t>71985</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>92514</t>
+          <t>103238</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -8176,17 +8176,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>408414</t>
+          <t>456073</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>408414</t>
+          <t>456073</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>408414</t>
+          <t>456073</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8211,17 +8211,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>408414</t>
+          <t>456073</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>408414</t>
+          <t>456073</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>408414</t>
+          <t>456073</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8258,32 +8258,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>192294</t>
+          <t>220157</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>166094</t>
+          <t>195760</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>214567</t>
+          <t>244848</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8293,32 +8293,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>192294</t>
+          <t>220157</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>166094</t>
+          <t>195760</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>214567</t>
+          <t>244848</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -8336,32 +8336,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>773205</t>
+          <t>733425</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>703746</t>
+          <t>699412</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>946025</t>
+          <t>771173</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8371,32 +8371,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>773205</t>
+          <t>733425</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>703746</t>
+          <t>699412</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>946025</t>
+          <t>771173</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -8414,32 +8414,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>577953</t>
+          <t>640087</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>515978</t>
+          <t>603152</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>623269</t>
+          <t>678393</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8449,32 +8449,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>577953</t>
+          <t>640087</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>515978</t>
+          <t>603152</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>623269</t>
+          <t>678393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -8492,32 +8492,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>398370</t>
+          <t>444518</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>352441</t>
+          <t>413546</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>433356</t>
+          <t>478319</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8527,32 +8527,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>398370</t>
+          <t>444518</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>352441</t>
+          <t>413546</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>433356</t>
+          <t>478319</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -8570,32 +8570,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>264354</t>
+          <t>292011</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>230110</t>
+          <t>266017</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>294198</t>
+          <t>321144</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8605,32 +8605,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>264354</t>
+          <t>292011</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>230110</t>
+          <t>266017</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>294198</t>
+          <t>321144</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -8648,17 +8648,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2206176</t>
+          <t>2330199</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2206176</t>
+          <t>2330199</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2206176</t>
+          <t>2330199</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8683,17 +8683,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2206176</t>
+          <t>2330199</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2206176</t>
+          <t>2330199</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2206176</t>
+          <t>2330199</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
